--- a/data/nzd0287/nzd0287.xlsx
+++ b/data/nzd0287/nzd0287.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W366"/>
+  <dimension ref="A1:W367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27918,6 +27918,81 @@
         <v>355.2</v>
       </c>
       <c r="W366" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>354.98</v>
+      </c>
+      <c r="C367" t="n">
+        <v>351.94</v>
+      </c>
+      <c r="D367" t="n">
+        <v>357.21</v>
+      </c>
+      <c r="E367" t="n">
+        <v>349.92</v>
+      </c>
+      <c r="F367" t="n">
+        <v>350.42</v>
+      </c>
+      <c r="G367" t="n">
+        <v>362.01</v>
+      </c>
+      <c r="H367" t="n">
+        <v>357.63</v>
+      </c>
+      <c r="I367" t="n">
+        <v>369.68</v>
+      </c>
+      <c r="J367" t="n">
+        <v>363.69</v>
+      </c>
+      <c r="K367" t="n">
+        <v>355.55</v>
+      </c>
+      <c r="L367" t="n">
+        <v>355.12</v>
+      </c>
+      <c r="M367" t="n">
+        <v>367</v>
+      </c>
+      <c r="N367" t="n">
+        <v>366.23</v>
+      </c>
+      <c r="O367" t="n">
+        <v>369.69</v>
+      </c>
+      <c r="P367" t="n">
+        <v>375.93</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>369.4</v>
+      </c>
+      <c r="R367" t="n">
+        <v>379.27</v>
+      </c>
+      <c r="S367" t="n">
+        <v>376.79</v>
+      </c>
+      <c r="T367" t="n">
+        <v>368.78</v>
+      </c>
+      <c r="U367" t="n">
+        <v>356.89</v>
+      </c>
+      <c r="V367" t="n">
+        <v>355.46</v>
+      </c>
+      <c r="W367" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27934,7 +28009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B368"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31617,6 +31692,16 @@
       </c>
       <c r="B368" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>-0.43</v>
       </c>
     </row>
   </sheetData>
@@ -31785,28 +31870,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1299994918110074</v>
+        <v>-0.1297027877261569</v>
       </c>
       <c r="J2" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K2" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07159545597503669</v>
+        <v>0.07172642155464504</v>
       </c>
       <c r="M2" t="n">
-        <v>2.637781833024187</v>
+        <v>2.632198349724326</v>
       </c>
       <c r="N2" t="n">
-        <v>12.15953272929869</v>
+        <v>12.12705051055306</v>
       </c>
       <c r="O2" t="n">
-        <v>3.487052154657095</v>
+        <v>3.482391493004923</v>
       </c>
       <c r="P2" t="n">
-        <v>357.9534988531649</v>
+        <v>357.9503787903337</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31863,28 +31948,28 @@
         <v>0.0311</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09090086432877123</v>
+        <v>-0.08988041735634096</v>
       </c>
       <c r="J3" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K3" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L3" t="n">
-        <v>0.034260908041163</v>
+        <v>0.03371397785229069</v>
       </c>
       <c r="M3" t="n">
-        <v>2.781507378107272</v>
+        <v>2.779059226798772</v>
       </c>
       <c r="N3" t="n">
-        <v>12.9234583209171</v>
+        <v>12.89690798463044</v>
       </c>
       <c r="O3" t="n">
-        <v>3.594921184242723</v>
+        <v>3.591226529283615</v>
       </c>
       <c r="P3" t="n">
-        <v>352.5837882406729</v>
+        <v>352.5730574862528</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31941,28 +32026,28 @@
         <v>0.0361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07923523238835962</v>
+        <v>0.07930230330747602</v>
       </c>
       <c r="J4" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K4" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0239955750461438</v>
+        <v>0.02419047405609509</v>
       </c>
       <c r="M4" t="n">
-        <v>2.943901781157943</v>
+        <v>2.936191659147994</v>
       </c>
       <c r="N4" t="n">
-        <v>14.16899592334582</v>
+        <v>14.13032066179613</v>
       </c>
       <c r="O4" t="n">
-        <v>3.764172674485831</v>
+        <v>3.759031878262823</v>
       </c>
       <c r="P4" t="n">
-        <v>354.9628227357276</v>
+        <v>354.9621174354218</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32019,28 +32104,28 @@
         <v>0.0411</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07769001721263111</v>
+        <v>0.07909681104022573</v>
       </c>
       <c r="J5" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K5" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02156198861069458</v>
+        <v>0.02245278033703846</v>
       </c>
       <c r="M5" t="n">
-        <v>3.084176027201244</v>
+        <v>3.082371841269992</v>
       </c>
       <c r="N5" t="n">
-        <v>15.19695992172411</v>
+        <v>15.17208637127447</v>
       </c>
       <c r="O5" t="n">
-        <v>3.898327836614579</v>
+        <v>3.895136245534226</v>
       </c>
       <c r="P5" t="n">
-        <v>345.349289818506</v>
+        <v>345.3344963412442</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32097,28 +32182,28 @@
         <v>0.0456</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1458734978986658</v>
+        <v>0.147701933454567</v>
       </c>
       <c r="J6" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K6" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08780801579424469</v>
+        <v>0.09017651403723648</v>
       </c>
       <c r="M6" t="n">
-        <v>2.809483456329625</v>
+        <v>2.810204860452423</v>
       </c>
       <c r="N6" t="n">
-        <v>12.2655396572159</v>
+        <v>12.26015051231812</v>
       </c>
       <c r="O6" t="n">
-        <v>3.50221924745095</v>
+        <v>3.501449772925226</v>
       </c>
       <c r="P6" t="n">
-        <v>343.2711933645654</v>
+        <v>343.2519660127742</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32175,28 +32260,28 @@
         <v>0.0468</v>
       </c>
       <c r="I7" t="n">
-        <v>0.145369789737737</v>
+        <v>0.1470971855502679</v>
       </c>
       <c r="J7" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K7" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L7" t="n">
-        <v>0.10032962778024</v>
+        <v>0.1028701318871532</v>
       </c>
       <c r="M7" t="n">
-        <v>2.696601003444644</v>
+        <v>2.698292321135981</v>
       </c>
       <c r="N7" t="n">
-        <v>10.51439578858551</v>
+        <v>10.51076887486022</v>
       </c>
       <c r="O7" t="n">
-        <v>3.242590906757358</v>
+        <v>3.242031596832489</v>
       </c>
       <c r="P7" t="n">
-        <v>355.0578616109777</v>
+        <v>355.0396967667955</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32253,28 +32338,28 @@
         <v>0.0413</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01691051302473257</v>
+        <v>-0.0157089443344554</v>
       </c>
       <c r="J8" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K8" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001213792315476692</v>
+        <v>0.001053551499875183</v>
       </c>
       <c r="M8" t="n">
-        <v>2.849740124466332</v>
+        <v>2.848295251671814</v>
       </c>
       <c r="N8" t="n">
-        <v>13.05640154526881</v>
+        <v>13.03287348509078</v>
       </c>
       <c r="O8" t="n">
-        <v>3.613364297336874</v>
+        <v>3.610107129309431</v>
       </c>
       <c r="P8" t="n">
-        <v>355.963623668828</v>
+        <v>355.9509882856259</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32331,28 +32416,28 @@
         <v>0.0415</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01594278824283962</v>
+        <v>0.01588061114545772</v>
       </c>
       <c r="J9" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K9" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009953682708854217</v>
+        <v>0.000994157902148185</v>
       </c>
       <c r="M9" t="n">
-        <v>3.129211937140901</v>
+        <v>3.120885288544497</v>
       </c>
       <c r="N9" t="n">
-        <v>14.15448404594039</v>
+        <v>14.11584311351156</v>
       </c>
       <c r="O9" t="n">
-        <v>3.762244548928257</v>
+        <v>3.757105683037351</v>
       </c>
       <c r="P9" t="n">
-        <v>369.3608027621415</v>
+        <v>369.3614566002934</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32409,28 +32494,28 @@
         <v>0.0443</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05025287845301608</v>
+        <v>0.04878389312167539</v>
       </c>
       <c r="J10" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K10" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007963055197994673</v>
+        <v>0.007549277989460146</v>
       </c>
       <c r="M10" t="n">
-        <v>3.463524114975219</v>
+        <v>3.46021149011976</v>
       </c>
       <c r="N10" t="n">
-        <v>17.45628342602683</v>
+        <v>17.4267413630362</v>
       </c>
       <c r="O10" t="n">
-        <v>4.178071735385455</v>
+        <v>4.174534867866861</v>
       </c>
       <c r="P10" t="n">
-        <v>364.9299999729225</v>
+        <v>364.9454474398298</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32487,28 +32572,28 @@
         <v>0.0429</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05026435626782285</v>
+        <v>0.04988966719568069</v>
       </c>
       <c r="J11" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K11" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01286985754466152</v>
+        <v>0.01276263147619994</v>
       </c>
       <c r="M11" t="n">
-        <v>2.624356113083176</v>
+        <v>2.618818060670588</v>
       </c>
       <c r="N11" t="n">
-        <v>10.75233291072466</v>
+        <v>10.72413594781804</v>
       </c>
       <c r="O11" t="n">
-        <v>3.279075008401707</v>
+        <v>3.274772655898123</v>
       </c>
       <c r="P11" t="n">
-        <v>354.8605864623706</v>
+        <v>354.8645265950043</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32565,28 +32650,28 @@
         <v>0.0355</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0125563187280317</v>
+        <v>-0.01370109169403366</v>
       </c>
       <c r="J12" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K12" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0006613340702940063</v>
+        <v>0.0007918683865874021</v>
       </c>
       <c r="M12" t="n">
-        <v>2.92647839749274</v>
+        <v>2.9245723807505</v>
       </c>
       <c r="N12" t="n">
-        <v>13.21898882640102</v>
+        <v>13.19389551905161</v>
       </c>
       <c r="O12" t="n">
-        <v>3.635792736997122</v>
+        <v>3.632340226224908</v>
       </c>
       <c r="P12" t="n">
-        <v>357.4748116563304</v>
+        <v>357.4868497904978</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32643,28 +32728,28 @@
         <v>0.0256</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1424069484516256</v>
+        <v>-0.1415759879454247</v>
       </c>
       <c r="J13" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K13" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04638188289572809</v>
+        <v>0.04614553633775742</v>
       </c>
       <c r="M13" t="n">
-        <v>3.652907456873438</v>
+        <v>3.646451163847914</v>
       </c>
       <c r="N13" t="n">
-        <v>23.13504015864143</v>
+        <v>23.07763820781191</v>
       </c>
       <c r="O13" t="n">
-        <v>4.809889828118876</v>
+        <v>4.803919046758793</v>
       </c>
       <c r="P13" t="n">
-        <v>369.367391864032</v>
+        <v>369.358653699908</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32721,28 +32806,28 @@
         <v>0.0262</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.02772687481328943</v>
+        <v>-0.0282764456551367</v>
       </c>
       <c r="J14" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K14" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002427368235032534</v>
+        <v>0.002540605465540025</v>
       </c>
       <c r="M14" t="n">
-        <v>3.338594294754123</v>
+        <v>3.332080222310655</v>
       </c>
       <c r="N14" t="n">
-        <v>17.53042654844128</v>
+        <v>17.48506990990582</v>
       </c>
       <c r="O14" t="n">
-        <v>4.18693522142883</v>
+        <v>4.181515264817985</v>
       </c>
       <c r="P14" t="n">
-        <v>367.940583270963</v>
+        <v>367.9463624147104</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32799,28 +32884,28 @@
         <v>0.0255</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1194405574084879</v>
+        <v>-0.1189149076599129</v>
       </c>
       <c r="J15" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K15" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04156849262865003</v>
+        <v>0.04147499374272456</v>
       </c>
       <c r="M15" t="n">
-        <v>3.327905042581815</v>
+        <v>3.321295129077125</v>
       </c>
       <c r="N15" t="n">
-        <v>18.25081352503766</v>
+        <v>18.20327225211499</v>
       </c>
       <c r="O15" t="n">
-        <v>4.272097087501368</v>
+        <v>4.266529298166717</v>
       </c>
       <c r="P15" t="n">
-        <v>371.9768969135744</v>
+        <v>371.9713693178097</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32877,28 +32962,28 @@
         <v>0.0261</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1390558560831151</v>
+        <v>-0.1389422554207012</v>
       </c>
       <c r="J16" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K16" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05202882178130175</v>
+        <v>0.05227397790294175</v>
       </c>
       <c r="M16" t="n">
-        <v>3.652867085904739</v>
+        <v>3.643447188896639</v>
       </c>
       <c r="N16" t="n">
-        <v>19.54841216354442</v>
+        <v>19.49510976090305</v>
       </c>
       <c r="O16" t="n">
-        <v>4.421358633219479</v>
+        <v>4.415326687902386</v>
       </c>
       <c r="P16" t="n">
-        <v>379.4738726685924</v>
+        <v>379.4726780736323</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32955,28 +33040,28 @@
         <v>0.0267</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1623934667659548</v>
+        <v>-0.1644435319455778</v>
       </c>
       <c r="J17" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K17" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08094088505509567</v>
+        <v>0.08316712287426087</v>
       </c>
       <c r="M17" t="n">
-        <v>3.263284331740308</v>
+        <v>3.26426519946895</v>
       </c>
       <c r="N17" t="n">
-        <v>16.61477188356918</v>
+        <v>16.60473058466824</v>
       </c>
       <c r="O17" t="n">
-        <v>4.076122162493315</v>
+        <v>4.074890254309708</v>
       </c>
       <c r="P17" t="n">
-        <v>377.3807320526776</v>
+        <v>377.4022900038322</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33033,28 +33118,28 @@
         <v>0.0328</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.03051968203792495</v>
+        <v>-0.03202291382696461</v>
       </c>
       <c r="J18" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K18" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L18" t="n">
-        <v>0.003372812515974655</v>
+        <v>0.003731830146651016</v>
       </c>
       <c r="M18" t="n">
-        <v>3.031278939733635</v>
+        <v>3.030558572030293</v>
       </c>
       <c r="N18" t="n">
-        <v>15.2715218460309</v>
+        <v>15.24880533077377</v>
       </c>
       <c r="O18" t="n">
-        <v>3.907879456435536</v>
+        <v>3.904971873237215</v>
       </c>
       <c r="P18" t="n">
-        <v>382.7398830886126</v>
+        <v>382.755690682344</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33111,28 +33196,28 @@
         <v>0.033</v>
       </c>
       <c r="I19" t="n">
-        <v>0.005096923476891456</v>
+        <v>0.003837834676209624</v>
       </c>
       <c r="J19" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K19" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L19" t="n">
-        <v>7.408728186508728e-05</v>
+        <v>4.225533538704251e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.127905337471715</v>
+        <v>3.12517548739658</v>
       </c>
       <c r="N19" t="n">
-        <v>19.45459378058218</v>
+        <v>19.41477495189529</v>
       </c>
       <c r="O19" t="n">
-        <v>4.410736194852531</v>
+        <v>4.406220029900378</v>
       </c>
       <c r="P19" t="n">
-        <v>378.868522890344</v>
+        <v>378.8817631400366</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33189,28 +33274,28 @@
         <v>0.036</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03552033157047266</v>
+        <v>0.03465610291301954</v>
       </c>
       <c r="J20" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K20" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003751590005892425</v>
+        <v>0.003594251050008102</v>
       </c>
       <c r="M20" t="n">
-        <v>3.255222674019944</v>
+        <v>3.250078246360638</v>
       </c>
       <c r="N20" t="n">
-        <v>18.59037165028937</v>
+        <v>18.54586123579263</v>
       </c>
       <c r="O20" t="n">
-        <v>4.311655326007561</v>
+        <v>4.306490593951487</v>
       </c>
       <c r="P20" t="n">
-        <v>369.3511471559342</v>
+        <v>369.3602351592665</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33267,28 +33352,28 @@
         <v>0.0526</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09962076681634173</v>
+        <v>0.09786882392351617</v>
       </c>
       <c r="J21" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K21" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03731413268166095</v>
+        <v>0.03622664355495842</v>
       </c>
       <c r="M21" t="n">
-        <v>2.848324964197968</v>
+        <v>2.847974770373918</v>
       </c>
       <c r="N21" t="n">
-        <v>14.20668608303986</v>
+        <v>14.19368940493104</v>
       </c>
       <c r="O21" t="n">
-        <v>3.769175782984903</v>
+        <v>3.767451314208459</v>
       </c>
       <c r="P21" t="n">
-        <v>357.3029874566257</v>
+        <v>357.3214104315071</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33345,28 +33430,28 @@
         <v>0.0488</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.03119672816398285</v>
+        <v>-0.03383085093640115</v>
       </c>
       <c r="J22" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K22" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L22" t="n">
-        <v>0.003847301415282778</v>
+        <v>0.004532285415492776</v>
       </c>
       <c r="M22" t="n">
-        <v>2.754576819837138</v>
+        <v>2.759525499383597</v>
       </c>
       <c r="N22" t="n">
-        <v>13.98200907547189</v>
+        <v>14.00217534021878</v>
       </c>
       <c r="O22" t="n">
-        <v>3.739252475491845</v>
+        <v>3.741948067547006</v>
       </c>
       <c r="P22" t="n">
-        <v>360.9407099878682</v>
+        <v>360.9684097364556</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33404,7 +33489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W366"/>
+  <dimension ref="A1:W367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76229,6 +76314,123 @@
         </is>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>-39.197029455610284,177.9202262387094</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>-39.197632275756725,177.91977309465278</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>-39.19826789139393,177.91940640968969</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-39.19884836683821,177.9189010953514</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>-39.19944588983986,177.91843591828075</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>-39.20010432015252,177.9182048777895</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-39.20078008749878,177.9180204202412</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-39.201480519730374,177.91802833674768</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>-39.202163574431154,177.9178311579943</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>-39.20284540907494,177.91761184961868</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>-39.203491712974056,177.9172859453897</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>-39.204170551115716,177.91706264230572</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>-39.20480651656766,177.9167028777639</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>-39.20546456127797,177.9164232862854</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>-39.20613489207926,177.91618331234545</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>-39.206770032967846,177.91580292694047</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>-39.20744987712559,177.9156085269959</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>-39.208100638406144,177.91529221879446</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>-39.20873888973212,177.91491421871376</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>-39.209367229404414,177.91449338539277</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>-39.21001956847539,177.91417774047486</t>
+        </is>
+      </c>
+      <c r="W367" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0287/nzd0287.xlsx
+++ b/data/nzd0287/nzd0287.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W367"/>
+  <dimension ref="A1:W369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27975,7 +27975,7 @@
         <v>375.93</v>
       </c>
       <c r="Q367" t="n">
-        <v>369.4</v>
+        <v>370.71</v>
       </c>
       <c r="R367" t="n">
         <v>379.27</v>
@@ -27993,6 +27993,156 @@
         <v>355.46</v>
       </c>
       <c r="W367" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:53:36+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>355</v>
+      </c>
+      <c r="C368" t="n">
+        <v>351.65</v>
+      </c>
+      <c r="D368" t="n">
+        <v>357.32</v>
+      </c>
+      <c r="E368" t="n">
+        <v>349.89</v>
+      </c>
+      <c r="F368" t="n">
+        <v>349.72</v>
+      </c>
+      <c r="G368" t="n">
+        <v>362.07</v>
+      </c>
+      <c r="H368" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="I368" t="n">
+        <v>370.1</v>
+      </c>
+      <c r="J368" t="n">
+        <v>363.91</v>
+      </c>
+      <c r="K368" t="n">
+        <v>355.18</v>
+      </c>
+      <c r="L368" t="n">
+        <v>355.5</v>
+      </c>
+      <c r="M368" t="n">
+        <v>367.56</v>
+      </c>
+      <c r="N368" t="n">
+        <v>366.66</v>
+      </c>
+      <c r="O368" t="n">
+        <v>370.85</v>
+      </c>
+      <c r="P368" t="n">
+        <v>377.39</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>372.48</v>
+      </c>
+      <c r="R368" t="n">
+        <v>380.39</v>
+      </c>
+      <c r="S368" t="n">
+        <v>377.87</v>
+      </c>
+      <c r="T368" t="n">
+        <v>368.93</v>
+      </c>
+      <c r="U368" t="n">
+        <v>357.44</v>
+      </c>
+      <c r="V368" t="n">
+        <v>355.86</v>
+      </c>
+      <c r="W368" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>354.72</v>
+      </c>
+      <c r="C369" t="n">
+        <v>350.94</v>
+      </c>
+      <c r="D369" t="n">
+        <v>357.41</v>
+      </c>
+      <c r="E369" t="n">
+        <v>349.84</v>
+      </c>
+      <c r="F369" t="n">
+        <v>349.88</v>
+      </c>
+      <c r="G369" t="n">
+        <v>362.13</v>
+      </c>
+      <c r="H369" t="n">
+        <v>357.77</v>
+      </c>
+      <c r="I369" t="n">
+        <v>370.79</v>
+      </c>
+      <c r="J369" t="n">
+        <v>364</v>
+      </c>
+      <c r="K369" t="n">
+        <v>355.16</v>
+      </c>
+      <c r="L369" t="n">
+        <v>355.44</v>
+      </c>
+      <c r="M369" t="n">
+        <v>367.58</v>
+      </c>
+      <c r="N369" t="n">
+        <v>367.03</v>
+      </c>
+      <c r="O369" t="n">
+        <v>370.42</v>
+      </c>
+      <c r="P369" t="n">
+        <v>377.22</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>372.57</v>
+      </c>
+      <c r="R369" t="n">
+        <v>380.45</v>
+      </c>
+      <c r="S369" t="n">
+        <v>377.73</v>
+      </c>
+      <c r="T369" t="n">
+        <v>368.51</v>
+      </c>
+      <c r="U369" t="n">
+        <v>357.21</v>
+      </c>
+      <c r="V369" t="n">
+        <v>355.74</v>
+      </c>
+      <c r="W369" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28009,7 +28159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B369"/>
+  <dimension ref="A1:B371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31702,6 +31852,26 @@
       </c>
       <c r="B369" t="n">
         <v>-0.43</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>
@@ -31870,28 +32040,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1297027877261569</v>
+        <v>-0.1292570941720504</v>
       </c>
       <c r="J2" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K2" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07172642155464504</v>
+        <v>0.0721318780960698</v>
       </c>
       <c r="M2" t="n">
-        <v>2.632198349724326</v>
+        <v>2.620313212055615</v>
       </c>
       <c r="N2" t="n">
-        <v>12.12705051055306</v>
+        <v>12.06209907167712</v>
       </c>
       <c r="O2" t="n">
-        <v>3.482391493004923</v>
+        <v>3.473053277978488</v>
       </c>
       <c r="P2" t="n">
-        <v>357.9503787903337</v>
+        <v>357.9456866332009</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31948,28 +32118,28 @@
         <v>0.0311</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08988041735634096</v>
+        <v>-0.08860650135066044</v>
       </c>
       <c r="J3" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K3" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03371397785229069</v>
+        <v>0.03319319444993762</v>
       </c>
       <c r="M3" t="n">
-        <v>2.779059226798772</v>
+        <v>2.77059851495805</v>
       </c>
       <c r="N3" t="n">
-        <v>12.89690798463044</v>
+        <v>12.83444007208941</v>
       </c>
       <c r="O3" t="n">
-        <v>3.591226529283615</v>
+        <v>3.582518677144533</v>
       </c>
       <c r="P3" t="n">
-        <v>352.5730574862528</v>
+        <v>352.5596457587901</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32026,28 +32196,28 @@
         <v>0.0361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07930230330747602</v>
+        <v>0.0796007593371203</v>
       </c>
       <c r="J4" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K4" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02419047405609509</v>
+        <v>0.02467967145556904</v>
       </c>
       <c r="M4" t="n">
-        <v>2.936191659147994</v>
+        <v>2.921704900185476</v>
       </c>
       <c r="N4" t="n">
-        <v>14.13032066179613</v>
+        <v>14.05391828365987</v>
       </c>
       <c r="O4" t="n">
-        <v>3.759031878262823</v>
+        <v>3.74885559653341</v>
       </c>
       <c r="P4" t="n">
-        <v>354.9621174354218</v>
+        <v>354.9589746346258</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32104,28 +32274,28 @@
         <v>0.0411</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07909681104022573</v>
+        <v>0.08178155852964344</v>
       </c>
       <c r="J5" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K5" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02245278033703846</v>
+        <v>0.02422427821596052</v>
       </c>
       <c r="M5" t="n">
-        <v>3.082371841269992</v>
+        <v>3.078267220187724</v>
       </c>
       <c r="N5" t="n">
-        <v>15.17208637127447</v>
+        <v>15.12046086264544</v>
       </c>
       <c r="O5" t="n">
-        <v>3.895136245534226</v>
+        <v>3.888503679134872</v>
       </c>
       <c r="P5" t="n">
-        <v>345.3344963412442</v>
+        <v>345.3062277344844</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32182,28 +32352,28 @@
         <v>0.0456</v>
       </c>
       <c r="I6" t="n">
-        <v>0.147701933454567</v>
+        <v>0.1505737553567479</v>
       </c>
       <c r="J6" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K6" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09017651403723648</v>
+        <v>0.09424918122744452</v>
       </c>
       <c r="M6" t="n">
-        <v>2.810204860452423</v>
+        <v>2.808008399019418</v>
       </c>
       <c r="N6" t="n">
-        <v>12.26015051231812</v>
+        <v>12.22882735118335</v>
       </c>
       <c r="O6" t="n">
-        <v>3.501449772925226</v>
+        <v>3.496974027810809</v>
       </c>
       <c r="P6" t="n">
-        <v>343.2519660127742</v>
+        <v>343.2217270690079</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32260,28 +32430,28 @@
         <v>0.0468</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1470971855502679</v>
+        <v>0.1505633522312765</v>
       </c>
       <c r="J7" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K7" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1028701318871532</v>
+        <v>0.1080304686771046</v>
       </c>
       <c r="M7" t="n">
-        <v>2.698292321135981</v>
+        <v>2.701654107890442</v>
       </c>
       <c r="N7" t="n">
-        <v>10.51076887486022</v>
+        <v>10.50503275598798</v>
       </c>
       <c r="O7" t="n">
-        <v>3.242031596832489</v>
+        <v>3.241146827280118</v>
       </c>
       <c r="P7" t="n">
-        <v>355.0396967667955</v>
+        <v>355.0032000150695</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32338,28 +32508,28 @@
         <v>0.0413</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0157089443344554</v>
+        <v>-0.01296292266493892</v>
       </c>
       <c r="J8" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K8" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001053551499875183</v>
+        <v>0.0007252447222982905</v>
       </c>
       <c r="M8" t="n">
-        <v>2.848295251671814</v>
+        <v>2.847187511663973</v>
       </c>
       <c r="N8" t="n">
-        <v>13.03287348509078</v>
+        <v>12.99455164361463</v>
       </c>
       <c r="O8" t="n">
-        <v>3.610107129309431</v>
+        <v>3.604795645194694</v>
       </c>
       <c r="P8" t="n">
-        <v>355.9509882856259</v>
+        <v>355.9220754810733</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32416,28 +32586,28 @@
         <v>0.0415</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01588061114545772</v>
+        <v>0.01661251874826474</v>
       </c>
       <c r="J9" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K9" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000994157902148185</v>
+        <v>0.001101834346317165</v>
       </c>
       <c r="M9" t="n">
-        <v>3.120885288544497</v>
+        <v>3.108310635637606</v>
       </c>
       <c r="N9" t="n">
-        <v>14.11584311351156</v>
+        <v>14.04206496968366</v>
       </c>
       <c r="O9" t="n">
-        <v>3.757105683037351</v>
+        <v>3.747274338727238</v>
       </c>
       <c r="P9" t="n">
-        <v>369.3614566002934</v>
+        <v>369.3537482796641</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32494,28 +32664,28 @@
         <v>0.0443</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04878389312167539</v>
+        <v>0.04621295663510974</v>
       </c>
       <c r="J10" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K10" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007549277989460146</v>
+        <v>0.006857043231380366</v>
       </c>
       <c r="M10" t="n">
-        <v>3.46021149011976</v>
+        <v>3.452081346730125</v>
       </c>
       <c r="N10" t="n">
-        <v>17.4267413630362</v>
+        <v>17.36031054404718</v>
       </c>
       <c r="O10" t="n">
-        <v>4.174534867866861</v>
+        <v>4.166570597511481</v>
       </c>
       <c r="P10" t="n">
-        <v>364.9454474398298</v>
+        <v>364.972517600889</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32572,28 +32742,28 @@
         <v>0.0429</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04988966719568069</v>
+        <v>0.04873054395111741</v>
       </c>
       <c r="J11" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K11" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01276263147619994</v>
+        <v>0.01233496158459657</v>
       </c>
       <c r="M11" t="n">
-        <v>2.618818060670588</v>
+        <v>2.609593034332029</v>
       </c>
       <c r="N11" t="n">
-        <v>10.72413594781804</v>
+        <v>10.67159901467602</v>
       </c>
       <c r="O11" t="n">
-        <v>3.274772655898123</v>
+        <v>3.266741344930146</v>
       </c>
       <c r="P11" t="n">
-        <v>354.8645265950043</v>
+        <v>354.8767314791186</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32650,28 +32820,28 @@
         <v>0.0355</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01370109169403366</v>
+        <v>-0.01554159785311913</v>
       </c>
       <c r="J12" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K12" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0007918683865874021</v>
+        <v>0.001030891138316337</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9245723807505</v>
+        <v>2.91840372371907</v>
       </c>
       <c r="N12" t="n">
-        <v>13.19389551905161</v>
+        <v>13.13668200069599</v>
       </c>
       <c r="O12" t="n">
-        <v>3.632340226224908</v>
+        <v>3.624456097222863</v>
       </c>
       <c r="P12" t="n">
-        <v>357.4868497904978</v>
+        <v>357.5062293460429</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32728,28 +32898,28 @@
         <v>0.0256</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1415759879454247</v>
+        <v>-0.1393159388419652</v>
       </c>
       <c r="J13" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K13" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04614553633775742</v>
+        <v>0.04526890453777355</v>
       </c>
       <c r="M13" t="n">
-        <v>3.646451163847914</v>
+        <v>3.636136655086896</v>
       </c>
       <c r="N13" t="n">
-        <v>23.07763820781191</v>
+        <v>22.97406232563973</v>
       </c>
       <c r="O13" t="n">
-        <v>4.803919046758793</v>
+        <v>4.79312657100141</v>
       </c>
       <c r="P13" t="n">
-        <v>369.358653699908</v>
+        <v>369.3348567164635</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32806,28 +32976,28 @@
         <v>0.0262</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0282764456551367</v>
+        <v>-0.02865621432557422</v>
       </c>
       <c r="J14" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K14" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002540605465540025</v>
+        <v>0.002643155638266226</v>
       </c>
       <c r="M14" t="n">
-        <v>3.332080222310655</v>
+        <v>3.315759465604383</v>
       </c>
       <c r="N14" t="n">
-        <v>17.48506990990582</v>
+        <v>17.39084039925547</v>
       </c>
       <c r="O14" t="n">
-        <v>4.181515264817985</v>
+        <v>4.170232655291005</v>
       </c>
       <c r="P14" t="n">
-        <v>367.9463624147104</v>
+        <v>367.950360204463</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32884,28 +33054,28 @@
         <v>0.0255</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1189149076599129</v>
+        <v>-0.1168344078390815</v>
       </c>
       <c r="J15" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K15" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04147499374272456</v>
+        <v>0.04055854822932514</v>
       </c>
       <c r="M15" t="n">
-        <v>3.321295129077125</v>
+        <v>3.313131682754999</v>
       </c>
       <c r="N15" t="n">
-        <v>18.20327225211499</v>
+        <v>18.12310891263118</v>
       </c>
       <c r="O15" t="n">
-        <v>4.266529298166717</v>
+        <v>4.257124488740161</v>
       </c>
       <c r="P15" t="n">
-        <v>371.9713693178097</v>
+        <v>371.9494640440334</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32962,28 +33132,28 @@
         <v>0.0261</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1389422554207012</v>
+        <v>-0.1371834559630758</v>
       </c>
       <c r="J16" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K16" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05227397790294175</v>
+        <v>0.05162754369928235</v>
       </c>
       <c r="M16" t="n">
-        <v>3.643447188896639</v>
+        <v>3.632424213071745</v>
       </c>
       <c r="N16" t="n">
-        <v>19.49510976090305</v>
+        <v>19.40242657872729</v>
       </c>
       <c r="O16" t="n">
-        <v>4.415326687902386</v>
+        <v>4.404818563655862</v>
       </c>
       <c r="P16" t="n">
-        <v>379.4726780736323</v>
+        <v>379.4541594243555</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33040,28 +33210,28 @@
         <v>0.0267</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1644435319455778</v>
+        <v>-0.1642140334509835</v>
       </c>
       <c r="J17" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K17" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08316712287426087</v>
+        <v>0.08404372686808081</v>
       </c>
       <c r="M17" t="n">
-        <v>3.26426519946895</v>
+        <v>3.245402833596419</v>
       </c>
       <c r="N17" t="n">
-        <v>16.60473058466824</v>
+        <v>16.49472486862161</v>
       </c>
       <c r="O17" t="n">
-        <v>4.074890254309708</v>
+        <v>4.061369826625201</v>
       </c>
       <c r="P17" t="n">
-        <v>377.4022900038322</v>
+        <v>377.3998834594578</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33118,28 +33288,28 @@
         <v>0.0328</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.03202291382696461</v>
+        <v>-0.03366983355353748</v>
       </c>
       <c r="J18" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K18" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L18" t="n">
-        <v>0.003731830146651016</v>
+        <v>0.004174638997943569</v>
       </c>
       <c r="M18" t="n">
-        <v>3.030558572030293</v>
+        <v>3.022332734039886</v>
       </c>
       <c r="N18" t="n">
-        <v>15.24880533077377</v>
+        <v>15.17753684677679</v>
       </c>
       <c r="O18" t="n">
-        <v>3.904971873237215</v>
+        <v>3.895835834166628</v>
       </c>
       <c r="P18" t="n">
-        <v>382.755690682344</v>
+        <v>382.7730315832148</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33196,28 +33366,28 @@
         <v>0.033</v>
       </c>
       <c r="I19" t="n">
-        <v>0.003837834676209624</v>
+        <v>0.002512331889652678</v>
       </c>
       <c r="J19" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K19" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L19" t="n">
-        <v>4.225533538704251e-05</v>
+        <v>1.833858893229845e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.12517548739658</v>
+        <v>3.114323226103546</v>
       </c>
       <c r="N19" t="n">
-        <v>19.41477495189529</v>
+        <v>19.31680262164657</v>
       </c>
       <c r="O19" t="n">
-        <v>4.406220029900378</v>
+        <v>4.395088465736107</v>
       </c>
       <c r="P19" t="n">
-        <v>378.8817631400366</v>
+        <v>378.8957202475505</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33274,28 +33444,28 @@
         <v>0.036</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03465610291301954</v>
+        <v>0.03289408020035536</v>
       </c>
       <c r="J20" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K20" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003594251050008102</v>
+        <v>0.00327918350794365</v>
       </c>
       <c r="M20" t="n">
-        <v>3.250078246360638</v>
+        <v>3.240038535009829</v>
       </c>
       <c r="N20" t="n">
-        <v>18.54586123579263</v>
+        <v>18.45858482980358</v>
       </c>
       <c r="O20" t="n">
-        <v>4.306490593951487</v>
+        <v>4.296345520300199</v>
       </c>
       <c r="P20" t="n">
-        <v>369.3602351592665</v>
+        <v>369.3787892608692</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33352,28 +33522,28 @@
         <v>0.0526</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09786882392351617</v>
+        <v>0.09492919202998858</v>
       </c>
       <c r="J21" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K21" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03622664355495842</v>
+        <v>0.03450164886621487</v>
       </c>
       <c r="M21" t="n">
-        <v>2.847974770373918</v>
+        <v>2.84498164415734</v>
       </c>
       <c r="N21" t="n">
-        <v>14.19368940493104</v>
+        <v>14.15358165772167</v>
       </c>
       <c r="O21" t="n">
-        <v>3.767451314208459</v>
+        <v>3.762124620174307</v>
       </c>
       <c r="P21" t="n">
-        <v>357.3214104315071</v>
+        <v>357.3523635584338</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33430,28 +33600,28 @@
         <v>0.0488</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.03383085093640115</v>
+        <v>-0.03858784491800785</v>
       </c>
       <c r="J22" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K22" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L22" t="n">
-        <v>0.004532285415492776</v>
+        <v>0.005924320109654269</v>
       </c>
       <c r="M22" t="n">
-        <v>2.759525499383597</v>
+        <v>2.767077106071997</v>
       </c>
       <c r="N22" t="n">
-        <v>14.00217534021878</v>
+        <v>14.02287560229631</v>
       </c>
       <c r="O22" t="n">
-        <v>3.741948067547006</v>
+        <v>3.744713020018532</v>
       </c>
       <c r="P22" t="n">
-        <v>360.9684097364556</v>
+        <v>361.0184982669416</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33489,7 +33659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W367"/>
+  <dimension ref="A1:W369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76397,7 +76567,7 @@
       </c>
       <c r="Q367" t="inlineStr">
         <is>
-          <t>-39.206770032967846,177.91580292694047</t>
+          <t>-39.2067736441379,177.9158173369432</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
@@ -76426,6 +76596,240 @@
         </is>
       </c>
       <c r="W367" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:53:36+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>-39.19702953416464,177.92022644659053</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>-39.19763113671133,177.91977008035343</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>-39.198268328993876,177.919407549565</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>-39.19884824032789,177.9189007891889</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>-39.19944318696126,177.9184286134415</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>-39.20010444965925,177.91820555084087</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>-39.20078065593228,177.91802696626752</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>-39.20148092899254,177.9180331615423</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>-39.20216378648365,177.91783368561642</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>-39.20284468086728,177.91760767763068</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>-39.203492885578505,177.9172900699452</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>-39.204172354049355,177.91706868461978</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>-39.204807827582364,177.9167075525217</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>-39.2054678435354,177.91643601051325</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>-39.20613895389823,177.91619935673566</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>-39.206778523349385,177.91583680694896</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>-39.207452854914315,177.91562089162028</t>
+        </is>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>-39.208103431487416,177.91530417265193</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>-39.20873927766348,177.9149158789861</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>-39.209368681516494,177.91449946151988</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>-39.21002064610997,177.91418215091312</t>
+        </is>
+      </c>
+      <c r="W368" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>-39.19702843440357,177.92022353625467</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>-39.19762834801367,177.91976270051754</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>-39.198268687030165,177.91940848219025</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>-39.198848029477354,177.9189002789181</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>-39.199443804762126,177.91843028311902</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>-39.20010457916597,177.91820622389227</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>-39.20078022711405,177.91802202803714</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>-39.20148160135136,177.91804108799064</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>-39.20216387323238,177.91783471964362</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>-39.20284464150469,177.91760745211784</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>-39.20349270043045,177.9172894186996</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>-39.20417241843983,177.9170689004167</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>-39.20480895566462,177.91671157498783</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>-39.2054666268367,177.91643129377348</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>-39.206138480946834,177.91619748855314</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>-39.206778771444796,177.91583779694932</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>-39.20745301443865,177.9156215540109</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>-39.208103069421405,177.91530262307776</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>-39.208738191455566,177.9149112302236</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>-39.20936807426967,177.914496920594</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>-39.2100203228196,177.91418082778165</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0287/nzd0287.xlsx
+++ b/data/nzd0287/nzd0287.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W369"/>
+  <dimension ref="A1:W371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28143,6 +28143,156 @@
         <v>355.74</v>
       </c>
       <c r="W369" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>355.72</v>
+      </c>
+      <c r="C370" t="n">
+        <v>351.5</v>
+      </c>
+      <c r="D370" t="n">
+        <v>357.83</v>
+      </c>
+      <c r="E370" t="n">
+        <v>350.25</v>
+      </c>
+      <c r="F370" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="G370" t="n">
+        <v>362.5</v>
+      </c>
+      <c r="H370" t="n">
+        <v>358.13</v>
+      </c>
+      <c r="I370" t="n">
+        <v>371.03</v>
+      </c>
+      <c r="J370" t="n">
+        <v>364.26</v>
+      </c>
+      <c r="K370" t="n">
+        <v>355.93</v>
+      </c>
+      <c r="L370" t="n">
+        <v>355.74</v>
+      </c>
+      <c r="M370" t="n">
+        <v>368.61</v>
+      </c>
+      <c r="N370" t="n">
+        <v>367.54</v>
+      </c>
+      <c r="O370" t="n">
+        <v>371.85</v>
+      </c>
+      <c r="P370" t="n">
+        <v>378.8</v>
+      </c>
+      <c r="Q370" t="n">
+        <v>374.4</v>
+      </c>
+      <c r="R370" t="n">
+        <v>381.87</v>
+      </c>
+      <c r="S370" t="n">
+        <v>377.73</v>
+      </c>
+      <c r="T370" t="n">
+        <v>368.51</v>
+      </c>
+      <c r="U370" t="n">
+        <v>357.21</v>
+      </c>
+      <c r="V370" t="n">
+        <v>355.74</v>
+      </c>
+      <c r="W370" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:53:59+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>354.49</v>
+      </c>
+      <c r="C371" t="n">
+        <v>350.4</v>
+      </c>
+      <c r="D371" t="n">
+        <v>356.65</v>
+      </c>
+      <c r="E371" t="n">
+        <v>349.18</v>
+      </c>
+      <c r="F371" t="n">
+        <v>348.34</v>
+      </c>
+      <c r="G371" t="n">
+        <v>361.24</v>
+      </c>
+      <c r="H371" t="n">
+        <v>357.07</v>
+      </c>
+      <c r="I371" t="n">
+        <v>369.3</v>
+      </c>
+      <c r="J371" t="n">
+        <v>362.14</v>
+      </c>
+      <c r="K371" t="n">
+        <v>354.19</v>
+      </c>
+      <c r="L371" t="n">
+        <v>353.83</v>
+      </c>
+      <c r="M371" t="n">
+        <v>366.39</v>
+      </c>
+      <c r="N371" t="n">
+        <v>366</v>
+      </c>
+      <c r="O371" t="n">
+        <v>371.06</v>
+      </c>
+      <c r="P371" t="n">
+        <v>378.88</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>373.85</v>
+      </c>
+      <c r="R371" t="n">
+        <v>381.75</v>
+      </c>
+      <c r="S371" t="n">
+        <v>376.98</v>
+      </c>
+      <c r="T371" t="n">
+        <v>367.56</v>
+      </c>
+      <c r="U371" t="n">
+        <v>356.01</v>
+      </c>
+      <c r="V371" t="n">
+        <v>356.07</v>
+      </c>
+      <c r="W371" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28159,7 +28309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B371"/>
+  <dimension ref="A1:B373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31872,6 +32022,26 @@
       </c>
       <c r="B371" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -32040,28 +32210,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1292570941720504</v>
+        <v>-0.1285379153785856</v>
       </c>
       <c r="J2" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K2" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0721318780960698</v>
+        <v>0.07222620378900968</v>
       </c>
       <c r="M2" t="n">
-        <v>2.620313212055615</v>
+        <v>2.610053323629879</v>
       </c>
       <c r="N2" t="n">
-        <v>12.06209907167712</v>
+        <v>12.00118052490478</v>
       </c>
       <c r="O2" t="n">
-        <v>3.473053277978488</v>
+        <v>3.464272005040133</v>
       </c>
       <c r="P2" t="n">
-        <v>357.9456866332009</v>
+        <v>357.9380908800684</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32118,28 +32288,28 @@
         <v>0.0311</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08860650135066044</v>
+        <v>-0.08773870349953346</v>
       </c>
       <c r="J3" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K3" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03319319444993762</v>
+        <v>0.0329646871904411</v>
       </c>
       <c r="M3" t="n">
-        <v>2.77059851495805</v>
+        <v>2.760108672354534</v>
       </c>
       <c r="N3" t="n">
-        <v>12.83444007208941</v>
+        <v>12.76997215491411</v>
       </c>
       <c r="O3" t="n">
-        <v>3.582518677144533</v>
+        <v>3.5735097810016</v>
       </c>
       <c r="P3" t="n">
-        <v>352.5596457587901</v>
+        <v>352.5504793604208</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32196,28 +32366,28 @@
         <v>0.0361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0796007593371203</v>
+        <v>0.07974473076249536</v>
       </c>
       <c r="J4" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K4" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02467967145556904</v>
+        <v>0.02507744972379922</v>
       </c>
       <c r="M4" t="n">
-        <v>2.921704900185476</v>
+        <v>2.909112527835918</v>
       </c>
       <c r="N4" t="n">
-        <v>14.05391828365987</v>
+        <v>13.97992657392616</v>
       </c>
       <c r="O4" t="n">
-        <v>3.74885559653341</v>
+        <v>3.738974000167179</v>
       </c>
       <c r="P4" t="n">
-        <v>354.9589746346258</v>
+        <v>354.9574564468177</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32274,28 +32444,28 @@
         <v>0.0411</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08178155852964344</v>
+        <v>0.08421101704768406</v>
       </c>
       <c r="J5" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K5" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02422427821596052</v>
+        <v>0.02592664947868395</v>
       </c>
       <c r="M5" t="n">
-        <v>3.078267220187724</v>
+        <v>3.07330242443798</v>
       </c>
       <c r="N5" t="n">
-        <v>15.12046086264544</v>
+        <v>15.06597496046886</v>
       </c>
       <c r="O5" t="n">
-        <v>3.888503679134872</v>
+        <v>3.881491332010013</v>
       </c>
       <c r="P5" t="n">
-        <v>345.3062277344844</v>
+        <v>345.2805606791723</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32352,28 +32522,28 @@
         <v>0.0456</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1505737553567479</v>
+        <v>0.1527034349755703</v>
       </c>
       <c r="J6" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K6" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09424918122744452</v>
+        <v>0.09763578699797526</v>
       </c>
       <c r="M6" t="n">
-        <v>2.808008399019418</v>
+        <v>2.802398259235695</v>
       </c>
       <c r="N6" t="n">
-        <v>12.22882735118335</v>
+        <v>12.18665721216817</v>
       </c>
       <c r="O6" t="n">
-        <v>3.496974027810809</v>
+        <v>3.490939302274986</v>
       </c>
       <c r="P6" t="n">
-        <v>343.2217270690079</v>
+        <v>343.1992292449867</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32430,28 +32600,28 @@
         <v>0.0468</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1505633522312765</v>
+        <v>0.1536541116015817</v>
       </c>
       <c r="J7" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K7" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1080304686771046</v>
+        <v>0.1128828669593203</v>
       </c>
       <c r="M7" t="n">
-        <v>2.701654107890442</v>
+        <v>2.703134111419631</v>
       </c>
       <c r="N7" t="n">
-        <v>10.50503275598798</v>
+        <v>10.49193179233824</v>
       </c>
       <c r="O7" t="n">
-        <v>3.241146827280118</v>
+        <v>3.239125158486198</v>
       </c>
       <c r="P7" t="n">
-        <v>355.0032000150695</v>
+        <v>354.9705460659928</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32508,28 +32678,28 @@
         <v>0.0413</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01296292266493892</v>
+        <v>-0.01072465675769757</v>
       </c>
       <c r="J8" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K8" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0007252447222982905</v>
+        <v>0.0005020805041850984</v>
       </c>
       <c r="M8" t="n">
-        <v>2.847187511663973</v>
+        <v>2.843357893280988</v>
       </c>
       <c r="N8" t="n">
-        <v>12.99455164361463</v>
+        <v>12.94760644496972</v>
       </c>
       <c r="O8" t="n">
-        <v>3.604795645194694</v>
+        <v>3.598278261192388</v>
       </c>
       <c r="P8" t="n">
-        <v>355.9220754810733</v>
+        <v>355.8984285175623</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32586,28 +32756,28 @@
         <v>0.0415</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01661251874826474</v>
+        <v>0.01701334159722236</v>
       </c>
       <c r="J9" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K9" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001101834346317165</v>
+        <v>0.001170198177017356</v>
       </c>
       <c r="M9" t="n">
-        <v>3.108310635637606</v>
+        <v>3.096649250015314</v>
       </c>
       <c r="N9" t="n">
-        <v>14.04206496968366</v>
+        <v>13.97093490631618</v>
       </c>
       <c r="O9" t="n">
-        <v>3.747274338727238</v>
+        <v>3.7377713822967</v>
       </c>
       <c r="P9" t="n">
-        <v>369.3537482796641</v>
+        <v>369.3495176032887</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32664,28 +32834,28 @@
         <v>0.0443</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04621295663510974</v>
+        <v>0.04287168664792838</v>
       </c>
       <c r="J10" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K10" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006857043231380366</v>
+        <v>0.005964623760801646</v>
       </c>
       <c r="M10" t="n">
-        <v>3.452081346730125</v>
+        <v>3.447240753341099</v>
       </c>
       <c r="N10" t="n">
-        <v>17.36031054404718</v>
+        <v>17.3210444635232</v>
       </c>
       <c r="O10" t="n">
-        <v>4.166570597511481</v>
+        <v>4.161855891729458</v>
       </c>
       <c r="P10" t="n">
-        <v>364.972517600889</v>
+        <v>365.0078271121702</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32742,28 +32912,28 @@
         <v>0.0429</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04873054395111741</v>
+        <v>0.0474740351669674</v>
       </c>
       <c r="J11" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K11" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01233496158459657</v>
+        <v>0.01185290098029024</v>
       </c>
       <c r="M11" t="n">
-        <v>2.609593034332029</v>
+        <v>2.600840043274676</v>
       </c>
       <c r="N11" t="n">
-        <v>10.67159901467602</v>
+        <v>10.62486422043556</v>
       </c>
       <c r="O11" t="n">
-        <v>3.266741344930146</v>
+        <v>3.259580374900358</v>
       </c>
       <c r="P11" t="n">
-        <v>354.8767314791186</v>
+        <v>354.8900122932064</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32820,28 +32990,28 @@
         <v>0.0355</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01554159785311913</v>
+        <v>-0.01809007444636343</v>
       </c>
       <c r="J12" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K12" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001030891138316337</v>
+        <v>0.001410749734686578</v>
       </c>
       <c r="M12" t="n">
-        <v>2.91840372371907</v>
+        <v>2.915928741576254</v>
       </c>
       <c r="N12" t="n">
-        <v>13.13668200069599</v>
+        <v>13.09880775593751</v>
       </c>
       <c r="O12" t="n">
-        <v>3.624456097222863</v>
+        <v>3.619227508175952</v>
       </c>
       <c r="P12" t="n">
-        <v>357.5062293460429</v>
+        <v>357.5331616081179</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32898,28 +33068,28 @@
         <v>0.0256</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1393159388419652</v>
+        <v>-0.1371835180229085</v>
       </c>
       <c r="J13" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K13" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04526890453777355</v>
+        <v>0.04445128208064786</v>
       </c>
       <c r="M13" t="n">
-        <v>3.636136655086896</v>
+        <v>3.625329379417694</v>
       </c>
       <c r="N13" t="n">
-        <v>22.97406232563973</v>
+        <v>22.87634119136177</v>
       </c>
       <c r="O13" t="n">
-        <v>4.79312657100141</v>
+        <v>4.782921825763178</v>
       </c>
       <c r="P13" t="n">
-        <v>369.3348567164635</v>
+        <v>369.312331106136</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32976,28 +33146,28 @@
         <v>0.0262</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.02865621432557422</v>
+        <v>-0.029101962318161</v>
       </c>
       <c r="J14" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K14" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002643155638266226</v>
+        <v>0.002760510627718871</v>
       </c>
       <c r="M14" t="n">
-        <v>3.315759465604383</v>
+        <v>3.301930171364651</v>
       </c>
       <c r="N14" t="n">
-        <v>17.39084039925547</v>
+        <v>17.30090187586687</v>
       </c>
       <c r="O14" t="n">
-        <v>4.170232655291005</v>
+        <v>4.15943528328869</v>
       </c>
       <c r="P14" t="n">
-        <v>367.950360204463</v>
+        <v>367.9550739513197</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33054,28 +33224,28 @@
         <v>0.0255</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1168344078390815</v>
+        <v>-0.1138968450052106</v>
       </c>
       <c r="J15" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K15" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04055854822932514</v>
+        <v>0.03902540129172472</v>
       </c>
       <c r="M15" t="n">
-        <v>3.313131682754999</v>
+        <v>3.309416388923658</v>
       </c>
       <c r="N15" t="n">
-        <v>18.12310891263118</v>
+        <v>18.06350690904776</v>
       </c>
       <c r="O15" t="n">
-        <v>4.257124488740161</v>
+        <v>4.250118458237107</v>
       </c>
       <c r="P15" t="n">
-        <v>371.9494640440334</v>
+        <v>371.9184275750883</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33132,28 +33302,28 @@
         <v>0.0261</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1371834559630758</v>
+        <v>-0.133766835841679</v>
       </c>
       <c r="J16" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K16" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05162754369928235</v>
+        <v>0.04969701561565787</v>
       </c>
       <c r="M16" t="n">
-        <v>3.632424213071745</v>
+        <v>3.629823703738137</v>
       </c>
       <c r="N16" t="n">
-        <v>19.40242657872729</v>
+        <v>19.34830135148674</v>
       </c>
       <c r="O16" t="n">
-        <v>4.404818563655862</v>
+        <v>4.398670407235207</v>
       </c>
       <c r="P16" t="n">
-        <v>379.4541594243555</v>
+        <v>379.4180589751736</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33210,28 +33380,28 @@
         <v>0.0267</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1642140334509835</v>
+        <v>-0.1629324248312788</v>
       </c>
       <c r="J17" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K17" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08404372686808081</v>
+        <v>0.08379726930397247</v>
       </c>
       <c r="M17" t="n">
-        <v>3.245402833596419</v>
+        <v>3.234111184791631</v>
       </c>
       <c r="N17" t="n">
-        <v>16.49472486862161</v>
+        <v>16.41311104740559</v>
       </c>
       <c r="O17" t="n">
-        <v>4.061369826625201</v>
+        <v>4.051309794054953</v>
       </c>
       <c r="P17" t="n">
-        <v>377.3998834594578</v>
+        <v>377.3863432962423</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33288,28 +33458,28 @@
         <v>0.0328</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.03366983355353748</v>
+        <v>-0.03372376597928605</v>
       </c>
       <c r="J18" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K18" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L18" t="n">
-        <v>0.004174638997943569</v>
+        <v>0.004242205403523824</v>
       </c>
       <c r="M18" t="n">
-        <v>3.022332734039886</v>
+        <v>3.006325823643318</v>
       </c>
       <c r="N18" t="n">
-        <v>15.17753684677679</v>
+        <v>15.09552794283008</v>
       </c>
       <c r="O18" t="n">
-        <v>3.895835834166628</v>
+        <v>3.885296377733632</v>
       </c>
       <c r="P18" t="n">
-        <v>382.7730315832148</v>
+        <v>382.7736017422209</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33366,28 +33536,28 @@
         <v>0.033</v>
       </c>
       <c r="I19" t="n">
-        <v>0.002512331889652678</v>
+        <v>0.0007313445625088895</v>
       </c>
       <c r="J19" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K19" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L19" t="n">
-        <v>1.833858893229845e-05</v>
+        <v>1.573069035032404e-06</v>
       </c>
       <c r="M19" t="n">
-        <v>3.114323226103546</v>
+        <v>3.105785487607541</v>
       </c>
       <c r="N19" t="n">
-        <v>19.31680262164657</v>
+        <v>19.22692174801632</v>
       </c>
       <c r="O19" t="n">
-        <v>4.395088465736107</v>
+        <v>4.38485139406301</v>
       </c>
       <c r="P19" t="n">
-        <v>378.8957202475505</v>
+        <v>378.9145401886842</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33444,28 +33614,28 @@
         <v>0.036</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03289408020035536</v>
+        <v>0.03042593420151668</v>
       </c>
       <c r="J20" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K20" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00327918350794365</v>
+        <v>0.002839020901542644</v>
       </c>
       <c r="M20" t="n">
-        <v>3.240038535009829</v>
+        <v>3.233069899435572</v>
       </c>
       <c r="N20" t="n">
-        <v>18.45858482980358</v>
+        <v>18.38648363821357</v>
       </c>
       <c r="O20" t="n">
-        <v>4.296345520300199</v>
+        <v>4.287946319418372</v>
       </c>
       <c r="P20" t="n">
-        <v>369.3787892608692</v>
+        <v>369.4048702739035</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33522,28 +33692,28 @@
         <v>0.0526</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09492919202998858</v>
+        <v>0.09127450244471344</v>
       </c>
       <c r="J21" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K21" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03450164886621487</v>
+        <v>0.03224910973738715</v>
       </c>
       <c r="M21" t="n">
-        <v>2.84498164415734</v>
+        <v>2.845260422214349</v>
       </c>
       <c r="N21" t="n">
-        <v>14.15358165772167</v>
+        <v>14.13705502990238</v>
       </c>
       <c r="O21" t="n">
-        <v>3.762124620174307</v>
+        <v>3.759927529873731</v>
       </c>
       <c r="P21" t="n">
-        <v>357.3523635584338</v>
+        <v>357.3909823182436</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33600,28 +33770,28 @@
         <v>0.0488</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.03858784491800785</v>
+        <v>-0.04308531063046062</v>
       </c>
       <c r="J22" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K22" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L22" t="n">
-        <v>0.005924320109654269</v>
+        <v>0.007423675417115416</v>
       </c>
       <c r="M22" t="n">
-        <v>2.767077106071997</v>
+        <v>2.773507613323479</v>
       </c>
       <c r="N22" t="n">
-        <v>14.02287560229631</v>
+        <v>14.03516570269277</v>
       </c>
       <c r="O22" t="n">
-        <v>3.744713020018532</v>
+        <v>3.746353654247389</v>
       </c>
       <c r="P22" t="n">
-        <v>361.0184982669416</v>
+        <v>361.0660179282411</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33659,7 +33829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W369"/>
+  <dimension ref="A1:W371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76835,6 +77005,240 @@
         </is>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>-39.19703236212129,177.92023393031178</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>-39.1976305475499,177.91976852123315</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>-39.19827035786615,177.9194128344416</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>-39.198849758451765,177.91890446313886</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>-39.19944465423826,177.9184325789256</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>-39.20010537779074,177.918210374376</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>-39.200780586124665,177.91802616236953</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>-39.20148183521517,177.91804384501617</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>-39.20216412383981,177.91783770683338</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>-39.202846156963716,177.9176161343632</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>-39.20349362617071,177.91729267492772</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>-39.20417573454901,177.91708001395932</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>-39.204810510588565,177.9167171194684</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>-39.205470673066486,177.91644697967604</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>-39.20614287661159,177.91621485166198</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>-39.206783816049494,177.91585792695793</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>-39.20745678984726,177.91563723058962</t>
+        </is>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>-39.208103069421405,177.91530262307776</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>-39.208738191455566,177.9149112302236</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>-39.20936807426967,177.914496920594</t>
+        </is>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>-39.2100203228196,177.91418082778165</t>
+        </is>
+      </c>
+      <c r="W370" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:53:59+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>-39.19702753102836,177.9202211456217</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>-39.19762622703201,177.91975708768496</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>-39.19826566361224,177.91940060668833</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>-39.198845246249874,177.91889354334361</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>-39.19943785842773,177.91841421247426</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>-39.20010265814905,177.91819624029665</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>-39.20077952903743,177.91801398905753</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>-39.20148014944537,177.91802397145736</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>-39.20216208042325,177.91781334974795</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>-39.202842732418986,177.91759651474428</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>-39.203487732289375,177.91727194360996</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>-39.20416858720547,177.91705606049968</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>-39.204805815327155,177.91670037731214</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>-39.20546843773702,177.91643831403738</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>-39.20614309917682,177.91621573080678</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>-39.206782299911865,177.9158518769551</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>-39.207456470798725,177.91563590580827</t>
+        </is>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>-39.20810112978165,177.91529432178785</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>-39.20873573455597,177.91490071516597</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>-39.20936490602439,177.91448366358983</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>-39.21002121186806,177.91418446639327</t>
+        </is>
+      </c>
+      <c r="W371" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
